--- a/output/pdf_financials_xlsx/GRI.xlsx
+++ b/output/pdf_financials_xlsx/GRI.xlsx
@@ -2000,13 +2000,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.627043</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.807104</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.949121</v>
       </c>
     </row>
     <row r="93">
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.794668</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.08890000000000001</v>
+        <v>-1.097831</v>
       </c>
     </row>
     <row r="119">
@@ -3248,7 +3248,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>1.627043</v>
       </c>
@@ -3628,7 +3632,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GRI.xlsx
+++ b/output/pdf_financials_xlsx/GRI.xlsx
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.6962970000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.467986</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.005795</v>
       </c>
     </row>
     <row r="35">
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.6962970000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.467986</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.005795</v>
       </c>
     </row>
     <row r="37">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.6962970000000001</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.499302</v>
+        <v>0.031316</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.05765</v>
+        <v>0.051855</v>
       </c>
     </row>
     <row r="49">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/GRI.xlsx
+++ b/output/pdf_financials_xlsx/GRI.xlsx
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007452</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.025876</v>
       </c>
     </row>
     <row r="112">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007452</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.025876</v>
       </c>
     </row>
     <row r="135">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.669276</v>
+        <v>-0.676728</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.6342410000000001</v>
+        <v>-0.660117</v>
       </c>
     </row>
   </sheetData>
@@ -3440,7 +3440,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -3696,7 +3700,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
